--- a/MATH/M07/bus123-math-m07-l01-starter.xlsx
+++ b/MATH/M07/bus123-math-m07-l01-starter.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R1b3003213b2d4e82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Ra18e731dee614adc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R09240e81f30f4034"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="Rda50d51b879444e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rcdbc33781bab4536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R35fabe95a40f4c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R5ea17215c9834815"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R6e28592a662847c2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1278,10 +1278,8 @@
           <x:t xml:space="preserve">Topic</x:t>
         </x:is>
       </x:c>
-      <x:c r="C6" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sales tax, excise tax, and property tax</x:t>
-        </x:is>
+      <x:c r="C6" s="7" t="str">
+        <x:v>Sales tax, excise tax, and property tax using a simplified training jurisdiction</x:v>
       </x:c>
       <x:c r="D6" s="3" t="n"/>
       <x:c r="E6" s="3" t="n"/>
@@ -1294,10 +1292,8 @@
           <x:t xml:space="preserve">Companies</x:t>
         </x:is>
       </x:c>
-      <x:c r="C7" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tidal Goods Co. and Meridian Advisory Group</x:t>
-        </x:is>
+      <x:c r="C7" s="7" t="str">
+        <x:v>Tidal Goods Co. and Meridian Advisory Group; supplied training rules</x:v>
       </x:c>
       <x:c r="D7" s="3" t="n"/>
       <x:c r="E7" s="3" t="n"/>
@@ -1310,10 +1306,8 @@
           <x:t xml:space="preserve">Live You Try It</x:t>
         </x:is>
       </x:c>
-      <x:c r="C8" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Self-graded Excel pauses during the slide presentation. Enter slide givens in the yellow input cells first, then build formulas.</x:t>
-        </x:is>
+      <x:c r="C8" s="7" t="str">
+        <x:v>Transfer practice with new numbers. Enter inputs, build formulas with cell references, and use formula-aware feedback.</x:v>
       </x:c>
       <x:c r="D8" s="3" t="n"/>
       <x:c r="E8" s="3" t="n"/>
@@ -1327,7 +1321,7 @@
         </x:is>
       </x:c>
       <x:c r="C9" s="18" t="str">
-        <x:v>Tax compliance audit. Begin in class and finish as homework: diagnose filings, repair formulas, recompute liabilities, and reconcile to the control total.</x:v>
+        <x:v>Tax compliance audit. Complete R01-R03 in pairs, choose one of R04-R06, then finish the remaining records for homework.</x:v>
       </x:c>
       <x:c r="D9" s="3" t="n"/>
       <x:c r="E9" s="3" t="n"/>
@@ -1340,10 +1334,8 @@
           <x:t xml:space="preserve">FormulaReferenceCard</x:t>
         </x:is>
       </x:c>
-      <x:c r="C10" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Syntax reminders after you decide which formula fits the business question.</x:t>
-        </x:is>
+      <x:c r="C10" s="7" t="str">
+        <x:v>Syntax reminders to use only after you decide which pattern fits the supplied business rule.</x:v>
       </x:c>
       <x:c r="D10" s="3" t="n"/>
       <x:c r="E10" s="3" t="n"/>
@@ -1415,7 +1407,7 @@
         <x:v>Yellow audit-repair cells</x:v>
       </x:c>
       <x:c r="C16" s="18" t="str">
-        <x:v>Only the yellow cells on Class Challenge are student work; blue-gray source records stay unchanged.</x:v>
+        <x:v>Only yellow cells are student work. Blue-gray source records and the supplied training-jurisdiction rules stay unchanged.</x:v>
       </x:c>
       <x:c r="D16" s="3" t="n"/>
       <x:c r="E16" s="3" t="n"/>
@@ -1479,10 +1471,8 @@
       <x:c r="K2" s="3" t="n"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the exact numbers from the slides. First enter the givens in the yellow input cells, then build the calculation in column H by referencing those cells.</x:t>
-        </x:is>
+      <x:c r="A3" s="10" t="str">
+        <x:v>Use the new numbers below. Enter the yellow inputs first, then build formulas in column H with the referenced cells. Feedback checks the value and confirms that a formula is present.</x:v>
       </x:c>
       <x:c r="B3" s="3" t="n"/>
       <x:c r="C3" s="3" t="n"/>
@@ -1574,10 +1564,8 @@
           <x:t xml:space="preserve">Sales tax</x:t>
         </x:is>
       </x:c>
-      <x:c r="C6" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">D: retail price 480; E: trade discount 80; H: taxable subtotal.</x:t>
-        </x:is>
+      <x:c r="C6" s="7" t="str">
+        <x:v>D: retail price 735; E: trade discount 95; H: taxable subtotal.</x:v>
       </x:c>
       <x:c r="D6" s="12" t="n"/>
       <x:c r="E6" s="12" t="n"/>
@@ -1585,18 +1573,14 @@
       <x:c r="G6" s="13" t="n"/>
       <x:c r="H6" s="12" t="n"/>
       <x:c r="I6" s="14" t="str">
-        <x:f>IF(COUNT(D6,E6,H6)&lt;3,"Enter the slide inputs and formula first",IF(AND(ABS(D6-480)&lt;=0.01,ABS(E6-80)&lt;=0.01,ABS(H6-400)&lt;=0.01),"Correct - inputs and cell references are working","Check: Subtract the discount before tax."))</x:f>
-        <x:v>Enter the slide inputs and formula first</x:v>
-      </x:c>
-      <x:c r="J6" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Subtract the discount before tax.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K6" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">slide 7</x:t>
-        </x:is>
+        <x:f>IF(COUNT(D6,E6,H6)&lt;3,"Enter the new inputs and a formula first",IF(IFERROR(NOT(ISFORMULA(H6)),FALSE),"Use a formula in H6 - do not type the answer",IF(AND(ABS(D6-735)&lt;=0.01,ABS(E6-95)&lt;=0.01,ABS(H6-640)&lt;=0.01),"Correct - value and formula are working","Check: subtract the discount before tax.")))</x:f>
+        <x:v>Enter the new inputs and a formula first</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="str">
+        <x:v>Subtract the discount before tax under the supplied rule.</x:v>
+      </x:c>
+      <x:c r="K6" s="7" t="str">
+        <x:v>slide 8</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1608,10 +1592,8 @@
           <x:t xml:space="preserve">Sales tax</x:t>
         </x:is>
       </x:c>
-      <x:c r="C7" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">E: tax rate 6%; H: tax owed using row 1 subtotal.</x:t>
-        </x:is>
+      <x:c r="C7" s="7" t="str">
+        <x:v>E: tax rate 5.75%; H: tax owed using row 1 subtotal.</x:v>
       </x:c>
       <x:c r="D7" s="13" t="n"/>
       <x:c r="E7" s="15" t="n"/>
@@ -1619,18 +1601,14 @@
       <x:c r="G7" s="13" t="n"/>
       <x:c r="H7" s="12" t="n"/>
       <x:c r="I7" s="14" t="str">
-        <x:f>IF(COUNT(H6,E7,H7)&lt;3,"Enter the slide inputs and formula first",IF(AND(ABS(E7-0.06)&lt;=5e-05,ABS(H7-24)&lt;=0.01),"Correct - inputs and cell references are working","Check: Use the taxable subtotal cell, not the retail price."))</x:f>
-        <x:v>Enter the slide inputs and formula first</x:v>
-      </x:c>
-      <x:c r="J7" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the taxable subtotal cell, not the retail price.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K7" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">slide 7</x:t>
-        </x:is>
+        <x:f>IF(COUNT(H6,E7,H7)&lt;3,"Enter the new inputs and a formula first",IF(IFERROR(NOT(ISFORMULA(H7)),FALSE),"Use a formula in H7 - do not type the answer",IF(AND(ABS(E7-0.0575)&lt;=5e-05,ABS(H7-36.8)&lt;=0.01),"Correct - value and formula are working","Check: use the taxable subtotal cell, not retail price.")))</x:f>
+        <x:v>Enter the new inputs and a formula first</x:v>
+      </x:c>
+      <x:c r="J7" s="7" t="str">
+        <x:v>Reference the taxable subtotal cell, not the retail price.</x:v>
+      </x:c>
+      <x:c r="K7" s="7" t="str">
+        <x:v>slide 8</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1642,10 +1620,8 @@
           <x:t xml:space="preserve">Sales tax</x:t>
         </x:is>
       </x:c>
-      <x:c r="C8" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">D: shipping 15; H: total price using rows 1 and 2.</x:t>
-        </x:is>
+      <x:c r="C8" s="7" t="str">
+        <x:v>D: shipping 22; H: total price using rows 1 and 2.</x:v>
       </x:c>
       <x:c r="D8" s="12" t="n"/>
       <x:c r="E8" s="13" t="n"/>
@@ -1653,18 +1629,14 @@
       <x:c r="G8" s="13" t="n"/>
       <x:c r="H8" s="12" t="n"/>
       <x:c r="I8" s="14" t="str">
-        <x:f>IF(COUNT(H6,H7,D8,H8)&lt;4,"Enter the slide inputs and formula first",IF(AND(ABS(D8-15)&lt;=0.01,ABS(H8-439)&lt;=0.01),"Correct - inputs and cell references are working","Check: Shipping is added after tax."))</x:f>
-        <x:v>Enter the slide inputs and formula first</x:v>
-      </x:c>
-      <x:c r="J8" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shipping is added after tax.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K8" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">slide 8</x:t>
-        </x:is>
+        <x:f>IF(COUNT(H6,H7,D8,H8)&lt;4,"Enter the new inputs and a formula first",IF(IFERROR(NOT(ISFORMULA(H8)),FALSE),"Use a formula in H8 - do not type the answer",IF(AND(ABS(D8-22)&lt;=0.01,ABS(H8-698.8)&lt;=0.01),"Correct - value and formula are working","Check: add shipping after the subtotal and tax.")))</x:f>
+        <x:v>Enter the new inputs and a formula first</x:v>
+      </x:c>
+      <x:c r="J8" s="7" t="str">
+        <x:v>Reference the subtotal and tax results, then add shipping.</x:v>
+      </x:c>
+      <x:c r="K8" s="7" t="str">
+        <x:v>slide 8</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1676,10 +1648,8 @@
           <x:t xml:space="preserve">Reverse tax</x:t>
         </x:is>
       </x:c>
-      <x:c r="C9" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">D: receipts 52,000; E: tax rate 6.5%; H: pre-tax sales.</x:t>
-        </x:is>
+      <x:c r="C9" s="7" t="str">
+        <x:v>D: receipts 64,200; E: tax rate 7%; H: pre-tax sales.</x:v>
       </x:c>
       <x:c r="D9" s="12" t="n"/>
       <x:c r="E9" s="15" t="n"/>
@@ -1687,18 +1657,14 @@
       <x:c r="G9" s="13" t="n"/>
       <x:c r="H9" s="12" t="n"/>
       <x:c r="I9" s="14" t="str">
-        <x:f>IF(COUNT(D9,E9,H9)&lt;3,"Enter the slide inputs and formula first",IF(AND(ABS(D9-52000)&lt;=0.01,ABS(E9-0.065)&lt;=5e-05,ABS(H9-48826.29)&lt;=0.01),"Correct - inputs and cell references are working","Check: Divide by 1 plus the tax rate."))</x:f>
-        <x:v>Enter the slide inputs and formula first</x:v>
-      </x:c>
-      <x:c r="J9" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Divide by 1 plus the tax rate.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K9" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">slide 10</x:t>
-        </x:is>
+        <x:f>IF(COUNT(D9,E9,H9)&lt;3,"Enter the new inputs and a formula first",IF(IFERROR(NOT(ISFORMULA(H9)),FALSE),"Use a formula in H9 - do not type the answer",IF(AND(ABS(D9-64200)&lt;=0.01,ABS(E9-0.07)&lt;=5e-05,ABS(H9-60000)&lt;=0.01),"Correct - value and formula are working","Check: divide receipts by 1 plus the rate.")))</x:f>
+        <x:v>Enter the new inputs and a formula first</x:v>
+      </x:c>
+      <x:c r="J9" s="7" t="str">
+        <x:v>Divide receipts by 1 plus the tax rate.</x:v>
+      </x:c>
+      <x:c r="K9" s="7" t="str">
+        <x:v>slide 8</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1710,10 +1676,8 @@
           <x:t xml:space="preserve">Reverse tax</x:t>
         </x:is>
       </x:c>
-      <x:c r="C10" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">H: tax held using row 4 receipts and pre-tax sales.</x:t>
-        </x:is>
+      <x:c r="C10" s="7" t="str">
+        <x:v>H: tax held using row 4 receipts and pre-tax sales.</x:v>
       </x:c>
       <x:c r="D10" s="13" t="n"/>
       <x:c r="E10" s="13" t="n"/>
@@ -1721,18 +1685,14 @@
       <x:c r="G10" s="13" t="n"/>
       <x:c r="H10" s="12" t="n"/>
       <x:c r="I10" s="14" t="str">
-        <x:f>IF(COUNT(D9,H9,H10)&lt;3,"Enter the slide inputs and formula first",IF(AND(ABS(H10-3173.71)&lt;=0.01),"Correct - inputs and cell references are working","Check: Receipts minus pre-tax sales."))</x:f>
-        <x:v>Enter the slide inputs and formula first</x:v>
-      </x:c>
-      <x:c r="J10" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Receipts minus pre-tax sales.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K10" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">slide 10</x:t>
-        </x:is>
+        <x:f>IF(COUNT(D9,H9,H10)&lt;3,"Enter the new inputs and a formula first",IF(IFERROR(NOT(ISFORMULA(H10)),FALSE),"Use a formula in H10 - do not type the answer",IF(AND(ABS(H10-4200)&lt;=0.01),"Correct - value and formula are working","Check: subtract pre-tax sales from receipts.")))</x:f>
+        <x:v>Enter the new inputs and a formula first</x:v>
+      </x:c>
+      <x:c r="J10" s="7" t="str">
+        <x:v>Reference receipts and pre-tax sales.</x:v>
+      </x:c>
+      <x:c r="K10" s="7" t="str">
+        <x:v>slide 8</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1744,10 +1704,8 @@
           <x:t xml:space="preserve">Excise tax</x:t>
         </x:is>
       </x:c>
-      <x:c r="C11" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">D: base cost 6,200; E: sales tax rate 7%; H: sales tax.</x:t>
-        </x:is>
+      <x:c r="C11" s="7" t="str">
+        <x:v>D: base cost 7,250; E: sales tax rate 6%; H: sales tax.</x:v>
       </x:c>
       <x:c r="D11" s="12" t="n"/>
       <x:c r="E11" s="15" t="n"/>
@@ -1755,18 +1713,14 @@
       <x:c r="G11" s="13" t="n"/>
       <x:c r="H11" s="12" t="n"/>
       <x:c r="I11" s="14" t="str">
-        <x:f>IF(COUNT(D11,E11,H11)&lt;3,"Enter the slide inputs and formula first",IF(AND(ABS(D11-6200)&lt;=0.01,ABS(E11-0.07)&lt;=5e-05,ABS(H11-434)&lt;=0.01),"Correct - inputs and cell references are working","Check: Both rates hit the base cost."))</x:f>
-        <x:v>Enter the slide inputs and formula first</x:v>
-      </x:c>
-      <x:c r="J11" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Both rates hit the base cost.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K11" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">slide 14</x:t>
-        </x:is>
+        <x:f>IF(COUNT(D11,E11,H11)&lt;3,"Enter the new inputs and a formula first",IF(IFERROR(NOT(ISFORMULA(H11)),FALSE),"Use a formula in H11 - do not type the answer",IF(AND(ABS(D11-7250)&lt;=0.01,ABS(E11-0.06)&lt;=5e-05,ABS(H11-435)&lt;=0.01),"Correct - value and formula are working","Check: both rates must point to the supplied base.")))</x:f>
+        <x:v>Enter the new inputs and a formula first</x:v>
+      </x:c>
+      <x:c r="J11" s="7" t="str">
+        <x:v>Reference the supplied base and sales-tax rate.</x:v>
+      </x:c>
+      <x:c r="K11" s="7" t="str">
+        <x:v>slide 13</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1778,10 +1732,8 @@
           <x:t xml:space="preserve">Excise tax</x:t>
         </x:is>
       </x:c>
-      <x:c r="C12" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">D: base cost 6,200; E: excise tax rate 8%; H: excise tax.</x:t>
-        </x:is>
+      <x:c r="C12" s="7" t="str">
+        <x:v>D: base cost 7,250; E: excise tax rate 4.5%; H: excise tax.</x:v>
       </x:c>
       <x:c r="D12" s="12" t="n"/>
       <x:c r="E12" s="15" t="n"/>
@@ -1789,18 +1741,14 @@
       <x:c r="G12" s="13" t="n"/>
       <x:c r="H12" s="12" t="n"/>
       <x:c r="I12" s="14" t="str">
-        <x:f>IF(COUNT(D12,E12,H12)&lt;3,"Enter the slide inputs and formula first",IF(AND(ABS(D12-6200)&lt;=0.01,ABS(E12-0.08)&lt;=5e-05,ABS(H12-496)&lt;=0.01),"Correct - inputs and cell references are working","Check: Do not apply excise to the tax-included cost."))</x:f>
-        <x:v>Enter the slide inputs and formula first</x:v>
-      </x:c>
-      <x:c r="J12" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Do not apply excise to the tax-included cost.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K12" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">slide 14</x:t>
-        </x:is>
+        <x:f>IF(COUNT(D12,E12,H12)&lt;3,"Enter the new inputs and a formula first",IF(IFERROR(NOT(ISFORMULA(H12)),FALSE),"Use a formula in H12 - do not type the answer",IF(AND(ABS(D12-7250)&lt;=0.01,ABS(E12-0.045)&lt;=5e-05,ABS(H12-326.25)&lt;=0.01),"Correct - value and formula are working","Check: use the base and excise rate, not a tax-included amount.")))</x:f>
+        <x:v>Enter the new inputs and a formula first</x:v>
+      </x:c>
+      <x:c r="J12" s="7" t="str">
+        <x:v>Reference the supplied base and excise-tax rate.</x:v>
+      </x:c>
+      <x:c r="K12" s="7" t="str">
+        <x:v>slide 13</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1812,10 +1760,8 @@
           <x:t xml:space="preserve">Excise tax</x:t>
         </x:is>
       </x:c>
-      <x:c r="C13" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">D: base cost 6,200; H: total cost using rows 6 and 7.</x:t>
-        </x:is>
+      <x:c r="C13" s="7" t="str">
+        <x:v>D: base cost 7,250; H: total cost using rows 6 and 7.</x:v>
       </x:c>
       <x:c r="D13" s="12" t="n"/>
       <x:c r="E13" s="13" t="n"/>
@@ -1823,18 +1769,14 @@
       <x:c r="G13" s="13" t="n"/>
       <x:c r="H13" s="12" t="n"/>
       <x:c r="I13" s="14" t="str">
-        <x:f>IF(COUNT(H11,H12,D13,H13)&lt;4,"Enter the slide inputs and formula first",IF(AND(ABS(D13-6200)&lt;=0.01,ABS(H13-7130)&lt;=0.01),"Correct - inputs and cell references are working","Check: Base plus both tax amounts."))</x:f>
-        <x:v>Enter the slide inputs and formula first</x:v>
-      </x:c>
-      <x:c r="J13" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Base plus both tax amounts.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K13" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">slide 15</x:t>
-        </x:is>
+        <x:f>IF(COUNT(D13,H11,H12,H13)&lt;4,"Enter the new inputs and a formula first",IF(IFERROR(NOT(ISFORMULA(H13)),FALSE),"Use a formula in H13 - do not type the answer",IF(AND(ABS(D13-7250)&lt;=0.01,ABS(H13-8011.25)&lt;=0.01),"Correct - value and formula are working","Check: add the base and both separate tax results.")))</x:f>
+        <x:v>Enter the new inputs and a formula first</x:v>
+      </x:c>
+      <x:c r="J13" s="7" t="str">
+        <x:v>Reference the base and both separate tax results.</x:v>
+      </x:c>
+      <x:c r="K13" s="7" t="str">
+        <x:v>slide 13</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1846,10 +1788,8 @@
           <x:t xml:space="preserve">Property tax</x:t>
         </x:is>
       </x:c>
-      <x:c r="C14" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">D: market value 820,000; E: assessment rate 40%; H: assessed value.</x:t>
-        </x:is>
+      <x:c r="C14" s="7" t="str">
+        <x:v>D: market value 540,000; E: assessment rate 32%; H: assessed value.</x:v>
       </x:c>
       <x:c r="D14" s="12" t="n"/>
       <x:c r="E14" s="15" t="n"/>
@@ -1857,18 +1797,14 @@
       <x:c r="G14" s="13" t="n"/>
       <x:c r="H14" s="12" t="n"/>
       <x:c r="I14" s="14" t="str">
-        <x:f>IF(COUNT(D14,E14,H14)&lt;3,"Enter the slide inputs and formula first",IF(AND(ABS(D14-820000)&lt;=0.01,ABS(E14-0.4)&lt;=5e-05,ABS(H14-328000)&lt;=0.01),"Correct - inputs and cell references are working","Check: Assessment rate times market value."))</x:f>
-        <x:v>Enter the slide inputs and formula first</x:v>
-      </x:c>
-      <x:c r="J14" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Assessment rate times market value.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K14" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">slide 20</x:t>
-        </x:is>
+        <x:f>IF(COUNT(D14,E14,H14)&lt;3,"Enter the new inputs and a formula first",IF(IFERROR(NOT(ISFORMULA(H14)),FALSE),"Use a formula in H14 - do not type the answer",IF(AND(ABS(D14-540000)&lt;=0.01,ABS(E14-0.32)&lt;=5e-05,ABS(H14-172800)&lt;=0.01),"Correct - value and formula are working","Check: multiply market value by the supplied assessment rate.")))</x:f>
+        <x:v>Enter the new inputs and a formula first</x:v>
+      </x:c>
+      <x:c r="J14" s="7" t="str">
+        <x:v>Reference market value and the supplied assessment rate.</x:v>
+      </x:c>
+      <x:c r="K14" s="7" t="str">
+        <x:v>slide 17</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1880,10 +1816,8 @@
           <x:t xml:space="preserve">Property tax</x:t>
         </x:is>
       </x:c>
-      <x:c r="C15" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">D: town budget 310,000; E: total assessed value 4,750,000; H: rounded rate.</x:t>
-        </x:is>
+      <x:c r="C15" s="7" t="str">
+        <x:v>D: town budget 234,500; E: total assessed value 3,450,000; H: rounded rate.</x:v>
       </x:c>
       <x:c r="D15" s="12" t="n"/>
       <x:c r="E15" s="12" t="n"/>
@@ -1891,18 +1825,14 @@
       <x:c r="G15" s="13" t="n"/>
       <x:c r="H15" s="16" t="n"/>
       <x:c r="I15" s="14" t="str">
-        <x:f>IF(COUNT(D15,E15,H15)&lt;3,"Enter the slide inputs and formula first",IF(AND(ABS(D15-310000)&lt;=0.01,ABS(E15-4750000)&lt;=0.01,ABS(H15-0.0653)&lt;=5e-05),"Correct - inputs and cell references are working","Check: Round the rate before applying it."))</x:f>
-        <x:v>Enter the slide inputs and formula first</x:v>
-      </x:c>
-      <x:c r="J15" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Round the rate before applying it.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K15" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">slide 20</x:t>
-        </x:is>
+        <x:f>IF(COUNT(D15,E15,H15)&lt;3,"Enter the new inputs and a formula first",IF(IFERROR(NOT(ISFORMULA(H15)),FALSE),"Use a formula in H15 - do not type the answer",IF(AND(ABS(D15-234500)&lt;=0.01,ABS(E15-3450000)&lt;=0.01,ABS(H15-0.068)&lt;=5e-05),"Correct - value and formula are working","Check: round budget divided by total assessed value to four decimals.")))</x:f>
+        <x:v>Enter the new inputs and a formula first</x:v>
+      </x:c>
+      <x:c r="J15" s="7" t="str">
+        <x:v>Use ROUND on budget divided by total assessed value.</x:v>
+      </x:c>
+      <x:c r="K15" s="7" t="str">
+        <x:v>slide 17</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1914,10 +1844,8 @@
           <x:t xml:space="preserve">Property tax</x:t>
         </x:is>
       </x:c>
-      <x:c r="C16" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">H: annual tax due using row 9 assessed value and row 10 rounded rate.</x:t>
-        </x:is>
+      <x:c r="C16" s="7" t="str">
+        <x:v>H: annual tax due using row 9 assessed value and row 10 rounded rate.</x:v>
       </x:c>
       <x:c r="D16" s="13" t="n"/>
       <x:c r="E16" s="13" t="n"/>
@@ -1925,18 +1853,14 @@
       <x:c r="G16" s="13" t="n"/>
       <x:c r="H16" s="12" t="n"/>
       <x:c r="I16" s="14" t="str">
-        <x:f>IF(COUNT(H14,H15,H16)&lt;3,"Enter the slide inputs and formula first",IF(AND(ABS(H16-21418.4)&lt;=0.01),"Correct - inputs and cell references are working","Check: Rounded tax rate times assessed value."))</x:f>
-        <x:v>Enter the slide inputs and formula first</x:v>
-      </x:c>
-      <x:c r="J16" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rounded tax rate times assessed value.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K16" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">slide 20</x:t>
-        </x:is>
+        <x:f>IF(COUNT(H14,H15,H16)&lt;3,"Enter the new inputs and a formula first",IF(IFERROR(NOT(ISFORMULA(H16)),FALSE),"Use a formula in H16 - do not type the answer",IF(AND(ABS(H16-11750.4)&lt;=0.01),"Correct - value and formula are working","Check: multiply assessed value by the rounded rate.")))</x:f>
+        <x:v>Enter the new inputs and a formula first</x:v>
+      </x:c>
+      <x:c r="J16" s="7" t="str">
+        <x:v>Reference the assessed value and rounded-rate results.</x:v>
+      </x:c>
+      <x:c r="K16" s="7" t="str">
+        <x:v>slide 17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1998,7 +1922,7 @@
     </x:row>
     <x:row r="3" ht="38" customHeight="1">
       <x:c r="A3" s="107" t="str">
-        <x:v>Begin in class; finish for homework. Audit each supplied filing, enter 0 for OK or 1 for ERROR, repair every formula, compute the adjustment, and reconcile to the control total.</x:v>
+        <x:v>Work in pairs: complete R01-R03, then choose one of R04-R06. Finish the remaining records for homework. Enter 0 for OK or 1 for ERROR, repair every formula, compute the adjustment, and reconcile to the control total.</x:v>
       </x:c>
       <x:c r="B3" s="107"/>
       <x:c r="C3" s="107"/>
@@ -2014,7 +1938,7 @@
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="110" t="str">
-        <x:v>Supplied fields are blue-gray and must not be changed. Yellow cells are your audit work. Click a corrected-liability cell to confirm that it contains a formula, not a typed answer.</x:v>
+        <x:v>All cases use the supplied training-jurisdiction rules. Blue-gray cells are source data and stay unchanged. Yellow cells are your audit work. Corrected liabilities must be formulas, not typed answers.</x:v>
       </x:c>
       <x:c r="B4" s="110"/>
       <x:c r="C4" s="110"/>
@@ -2552,10 +2476,8 @@
           <x:t xml:space="preserve">Finds the amount subject to sales tax.</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Apply discounts before tax.</x:t>
-        </x:is>
+      <x:c r="D4" s="7" t="str">
+        <x:v>Apply qualifying discounts before tax under the supplied rule.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2574,10 +2496,8 @@
           <x:t xml:space="preserve">Calculates the tax on the taxable subtotal.</x:t>
         </x:is>
       </x:c>
-      <x:c r="D5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the tax rate as a decimal.</x:t>
-        </x:is>
+      <x:c r="D5" s="7" t="str">
+        <x:v>Use the tax rate as a decimal and the taxable subtotal as the base.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2596,10 +2516,8 @@
           <x:t xml:space="preserve">Adds taxable amount, tax, and shipping.</x:t>
         </x:is>
       </x:c>
-      <x:c r="D6" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shipping rules can vary by scenario.</x:t>
-        </x:is>
+      <x:c r="D6" s="7" t="str">
+        <x:v>Add shipping after tax under the supplied rule.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2618,10 +2536,8 @@
           <x:t xml:space="preserve">Finds sales before tax from total receipts.</x:t>
         </x:is>
       </x:c>
-      <x:c r="D7" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Do not subtract the tax rate directly.</x:t>
-        </x:is>
+      <x:c r="D7" s="7" t="str">
+        <x:v>Do not divide receipts by the tax rate alone.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2640,10 +2556,8 @@
           <x:t xml:space="preserve">Finds tax collected and owed to the government.</x:t>
         </x:is>
       </x:c>
-      <x:c r="D8" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collected tax is not revenue.</x:t>
-        </x:is>
+      <x:c r="D8" s="7" t="str">
+        <x:v>Collected tax is a liability, not revenue.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2662,10 +2576,8 @@
           <x:t xml:space="preserve">Calculates both tax amounts from the same base.</x:t>
         </x:is>
       </x:c>
-      <x:c r="D9" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Do not compound the two rates.</x:t>
-        </x:is>
+      <x:c r="D9" s="7" t="str">
+        <x:v>Use only when the scenario says both taxes share one base.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2684,10 +2596,8 @@
           <x:t xml:space="preserve">Combines rates when they share one base.</x:t>
         </x:is>
       </x:c>
-      <x:c r="D10" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Only use when both taxes share the same base.</x:t>
-        </x:is>
+      <x:c r="D10" s="7" t="str">
+        <x:v>The shortcut is valid only under the supplied same-base rule.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2706,10 +2616,8 @@
           <x:t xml:space="preserve">Converts market value to taxable assessed value.</x:t>
         </x:is>
       </x:c>
-      <x:c r="D11" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use assessed value for tax due.</x:t>
-        </x:is>
+      <x:c r="D11" s="7" t="str">
+        <x:v>Use the assessment rule supplied by the training municipality.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2728,10 +2636,8 @@
           <x:t xml:space="preserve">Rounds the municipal tax rate to four decimals.</x:t>
         </x:is>
       </x:c>
-      <x:c r="D12" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Round before applying the rate.</x:t>
-        </x:is>
+      <x:c r="D12" s="7" t="str">
+        <x:v>Round the rate before applying it to assessed value.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2750,10 +2656,8 @@
           <x:t xml:space="preserve">Calculates annual property tax due.</x:t>
         </x:is>
       </x:c>
-      <x:c r="D13" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the rounded rate.</x:t>
-        </x:is>
+      <x:c r="D13" s="7" t="str">
+        <x:v>Use assessed value and the rounded rate.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2772,10 +2676,8 @@
           <x:t xml:space="preserve">Converts annual property tax into monthly planning cost.</x:t>
         </x:is>
       </x:c>
-      <x:c r="D14" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Useful for lease cash-flow planning.</x:t>
-        </x:is>
+      <x:c r="D14" s="7" t="str">
+        <x:v>Use for lease cash-flow planning; actual obligations depend on lease terms.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
